--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260807.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260807.xlsx
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>8,603,956</t>
+          <t>257,642,136</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>257,642,136</t>
+          <t>8,603,956</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>15,763,673</t>
+          <t>70,528,470</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>70,528,470</t>
+          <t>15,763,673</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,873,362</t>
+          <t>1,331,528</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1,331,528</t>
+          <t>17,799,662</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>17,799,662</t>
+          <t>1,873,362</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>10,786,740</t>
+          <t>1,846,788</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,846,788</t>
+          <t>10,786,740</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>25,536,884</t>
+          <t>5,003,102</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>5,003,102</t>
+          <t>25,536,884</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
